--- a/data/trans_dic/IP1003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen Alergias crónicas</t>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,61</t>
+          <t>4,46; 13,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,1</t>
+          <t>2,12; 10,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 13,75</t>
+          <t>3,6; 13,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,2</t>
+          <t>2,68; 10,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,73</t>
+          <t>1,41; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,4</t>
+          <t>0,69; 6,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,85</t>
+          <t>0,68; 6,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 13,93</t>
+          <t>4,12; 13,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 9,71</t>
+          <t>4,05; 9,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,09</t>
+          <t>1,82; 6,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,58</t>
+          <t>2,68; 8,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,2</t>
+          <t>4,63; 10,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 13,36</t>
+          <t>3,75; 13,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,79</t>
+          <t>0,84; 7,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,09</t>
+          <t>0,85; 6,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 10,59</t>
+          <t>2,22; 10,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,76</t>
+          <t>3,51; 12,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,0</t>
+          <t>1,38; 8,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 10,03</t>
+          <t>2,38; 9,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 14,41</t>
+          <t>3,97; 15,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,3</t>
+          <t>4,67; 10,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,25</t>
+          <t>1,79; 6,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,85</t>
+          <t>2,3; 6,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 11,28</t>
+          <t>3,64; 10,53</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,31</t>
+          <t>2,13; 12,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,18</t>
+          <t>0,84; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,38</t>
+          <t>0,89; 7,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,15</t>
+          <t>2,89; 15,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 14,76</t>
+          <t>5,13; 14,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,7</t>
+          <t>1,82; 10,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 18,32</t>
+          <t>3,08; 17,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,53</t>
+          <t>5,14; 12,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,23</t>
+          <t>0,89; 5,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,78</t>
+          <t>2,05; 8,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 14,33</t>
+          <t>4,18; 14,14</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,01</t>
+          <t>2,31; 6,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,4</t>
+          <t>1,68; 6,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,56</t>
+          <t>2,87; 7,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,16</t>
+          <t>3,82; 10,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,23</t>
+          <t>4,02; 9,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 14,41</t>
+          <t>7,55; 14,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,79</t>
+          <t>2,76; 7,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,41</t>
+          <t>3,81; 11,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,19</t>
+          <t>3,58; 7,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,52</t>
+          <t>5,42; 9,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,71</t>
+          <t>3,33; 6,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,15</t>
+          <t>4,49; 8,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,26</t>
+          <t>4,31; 12,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,79</t>
+          <t>5,13; 13,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,14</t>
+          <t>2,72; 9,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,1</t>
+          <t>1,92; 8,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,35</t>
+          <t>2,35; 8,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,09</t>
+          <t>2,82; 9,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,19</t>
+          <t>2,01; 8,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 17,75</t>
+          <t>7,32; 17,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,71</t>
+          <t>3,64; 8,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,85</t>
+          <t>4,78; 9,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,38</t>
+          <t>2,82; 7,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,03</t>
+          <t>5,9; 12,58</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,87</t>
+          <t>1,82; 10,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 11,49</t>
+          <t>1,01; 9,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,41</t>
+          <t>0,95; 8,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 17,7</t>
+          <t>5,66; 17,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,18</t>
+          <t>1,33; 10,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,15; 14,46</t>
+          <t>3,17; 15,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,54</t>
+          <t>3,31; 14,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,68</t>
+          <t>5,02; 12,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,66</t>
+          <t>1,12; 6,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,92</t>
+          <t>3,02; 10,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,88</t>
+          <t>3,05; 9,81</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,72</t>
+          <t>4,67; 7,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,91</t>
+          <t>3,36; 6,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,26</t>
+          <t>3,49; 6,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,11</t>
+          <t>4,07; 7,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,29</t>
+          <t>5,18; 8,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,49</t>
+          <t>4,5; 7,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,21</t>
+          <t>3,6; 6,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,66</t>
+          <t>6,73; 10,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,53</t>
+          <t>5,35; 7,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,35</t>
+          <t>4,33; 6,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,78</t>
+          <t>3,82; 5,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,39</t>
+          <t>5,82; 8,47</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8661</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11308</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12734</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6331</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17122</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4658; 13585</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1874; 9457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2990; 11411</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2781; 10660</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1376; 8207</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>621; 5549</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>677; 6228</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5631; 19004</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8176; 19162</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3242; 12310</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4899; 14981</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11111; 25810</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2787</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5759</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12386</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6826</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12238</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11816</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>777; 6755</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>898; 6703</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2105; 10203</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3019; 11142</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1326; 7871</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10964</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3790; 14587</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8094; 18226</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3361; 12073</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5028; 14512</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6926; 20038</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3903</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2857</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9151</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9294</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1439; 8207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>711; 6707</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>552; 4734</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8152</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5096; 14682</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4619</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1370; 7661</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1970; 11478</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8577; 20253</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1528; 9275</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2817; 11228</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4839; 16363</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8379</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7072</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11195</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14492</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12699</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24224</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>21079</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31296</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21123</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28590</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4645; 13942</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3448; 13041</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6416; 17488</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8320; 22894</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8129; 19456</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17140; 32158</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5811; 16675</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8281; 24182</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>14409; 29226</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23442; 41683</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14475; 29353</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>19525; 38821</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7864</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4944</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7539</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18737</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>13657</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13513</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23682</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4490; 13135</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7647; 19737</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3709; 13053</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2285; 10208</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2992; 10524</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3948; 12994</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2876; 11786</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11878; 28059</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8419; 20154</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13824; 28060</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7871; 20431</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16593; 35355</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2436</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5402</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>11577</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1359; 7772</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4046</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>615; 6044</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>658; 6011</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4098; 12736</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>983; 7549</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2147; 10270</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2387; 10134</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>7387; 17819</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1432; 8858</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3890; 13382</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4296; 13819</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>39057</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>30550</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>31485</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>36129</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45430</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>42275</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>33914</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>62635</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>84487</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>72825</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>65399</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98764</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>29827; 48869</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22595; 41834</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>23419; 40785</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26689; 47882</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>35479; 56781</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>32140; 53684</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>25557; 43287</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>50321; 80682</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>70806; 99727</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>60111; 88177</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>52722; 78920</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>81694; 118814</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,02</t>
+          <t>4,44; 13,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,69</t>
+          <t>2,04; 10,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,73</t>
+          <t>3,39; 13,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,29</t>
+          <t>2,77; 10,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,41</t>
+          <t>1,42; 8,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,18</t>
+          <t>0,69; 6,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,24</t>
+          <t>0,66; 6,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 13,92</t>
+          <t>4,34; 13,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,49</t>
+          <t>3,97; 9,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,91</t>
+          <t>1,56; 6,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,19</t>
+          <t>2,58; 8,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,75</t>
+          <t>4,47; 10,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 13,52</t>
+          <t>4,13; 13,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,33</t>
+          <t>0,76; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,34</t>
+          <t>0,61; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,78</t>
+          <t>2,07; 10,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 12,96</t>
+          <t>2,99; 12,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,19</t>
+          <t>1,54; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,72</t>
+          <t>2,09; 9,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 15,26</t>
+          <t>3,64; 14,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,51</t>
+          <t>4,49; 10,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,41</t>
+          <t>1,8; 6,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,64</t>
+          <t>2,19; 6,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,53</t>
+          <t>3,68; 10,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,18</t>
+          <t>2,02; 11,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,97</t>
+          <t>0,93; 8,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,66</t>
+          <t>0,88; 8,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 15,72</t>
+          <t>2,71; 16,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 14,78</t>
+          <t>4,92; 14,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,16</t>
+          <t>2,51; 11,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 17,98</t>
+          <t>3,14; 18,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,15</t>
+          <t>4,69; 11,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,42</t>
+          <t>1,19; 5,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,18</t>
+          <t>1,96; 7,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 14,14</t>
+          <t>4,33; 14,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,95</t>
+          <t>2,25; 6,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,34</t>
+          <t>1,67; 6,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,82</t>
+          <t>3,07; 7,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 10,5</t>
+          <t>3,91; 10,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,63</t>
+          <t>3,96; 9,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,17</t>
+          <t>7,66; 14,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,91</t>
+          <t>2,67; 7,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,13</t>
+          <t>3,92; 10,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,26</t>
+          <t>3,58; 7,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,64</t>
+          <t>5,35; 9,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,76</t>
+          <t>3,46; 7,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,92</t>
+          <t>4,66; 9,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,62</t>
+          <t>4,26; 12,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,23</t>
+          <t>4,93; 13,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,58</t>
+          <t>2,69; 9,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,59</t>
+          <t>1,88; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,27</t>
+          <t>2,09; 8,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,29</t>
+          <t>2,87; 9,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,24</t>
+          <t>1,88; 8,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 17,3</t>
+          <t>7,27; 17,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,71</t>
+          <t>3,65; 9,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,71</t>
+          <t>4,91; 9,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,32</t>
+          <t>3,01; 8,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,58</t>
+          <t>5,84; 12,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,38</t>
+          <t>1,81; 10,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,89</t>
+          <t>1,02; 10,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,72</t>
+          <t>0,94; 8,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 17,59</t>
+          <t>5,62; 17,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,2</t>
+          <t>1,32; 11,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 15,14</t>
+          <t>3,11; 15,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 14,07</t>
+          <t>3,43; 14,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,1</t>
+          <t>4,92; 12,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,92</t>
+          <t>1,14; 6,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,38</t>
+          <t>2,65; 10,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,81</t>
+          <t>2,92; 9,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,65</t>
+          <t>4,73; 7,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,21</t>
+          <t>3,24; 5,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,07</t>
+          <t>3,35; 6,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,3</t>
+          <t>4,13; 7,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,29</t>
+          <t>5,31; 8,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,52</t>
+          <t>4,54; 7,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,1</t>
+          <t>3,46; 6,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,79</t>
+          <t>6,61; 10,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,54</t>
+          <t>5,26; 7,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,36</t>
+          <t>4,34; 6,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,71</t>
+          <t>3,87; 5,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,47</t>
+          <t>5,81; 8,38</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4658; 13585</t>
+          <t>4629; 13575</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1874; 9457</t>
+          <t>1803; 8979</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2990; 11411</t>
+          <t>2821; 11167</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2781; 10660</t>
+          <t>2873; 10581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1376; 8207</t>
+          <t>1386; 8366</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>621; 5549</t>
+          <t>617; 5595</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>677; 6228</t>
+          <t>658; 6627</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5631; 19004</t>
+          <t>5922; 18265</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8176; 19162</t>
+          <t>8009; 19113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3242; 12310</t>
+          <t>2786; 11556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4899; 14981</t>
+          <t>4727; 15322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11111; 25810</t>
+          <t>10725; 25860</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3278; 11816</t>
+          <t>3611; 11890</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>777; 6755</t>
+          <t>704; 7064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>898; 6703</t>
+          <t>649; 6501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2105; 10203</t>
+          <t>1961; 9718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3019; 11142</t>
+          <t>2570; 10316</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1326; 7871</t>
+          <t>1478; 7986</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2686; 10964</t>
+          <t>2353; 10705</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3790; 14587</t>
+          <t>3475; 14165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8094; 18226</t>
+          <t>7785; 18408</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3361; 12073</t>
+          <t>3384; 11700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5028; 14512</t>
+          <t>4793; 14034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6926; 20038</t>
+          <t>6996; 19828</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1439; 8207</t>
+          <t>1364; 7472</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>711; 6707</t>
+          <t>785; 6945</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>552; 4734</t>
+          <t>547; 5020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1499; 8152</t>
+          <t>1403; 8307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5096; 14682</t>
+          <t>4885; 14368</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4619</t>
+          <t>0; 5166</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1370; 7661</t>
+          <t>1892; 8356</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1970; 11478</t>
+          <t>2007; 11901</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8577; 20253</t>
+          <t>7825; 19864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1528; 9275</t>
+          <t>2040; 9385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2817; 11228</t>
+          <t>2687; 10596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4839; 16363</t>
+          <t>5016; 16552</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4645; 13942</t>
+          <t>4525; 13746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448; 13041</t>
+          <t>3441; 12734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6416; 17488</t>
+          <t>6861; 17504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8320; 22894</t>
+          <t>8520; 22513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8129; 19456</t>
+          <t>8007; 19101</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17140; 32158</t>
+          <t>17371; 32655</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5811; 16675</t>
+          <t>5625; 16454</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8281; 24182</t>
+          <t>8513; 22941</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14409; 29226</t>
+          <t>14422; 29080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23442; 41683</t>
+          <t>23136; 41230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14475; 29353</t>
+          <t>15051; 30692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19525; 38821</t>
+          <t>20282; 40399</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4490; 13135</t>
+          <t>4433; 13150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7647; 19737</t>
+          <t>7354; 19912</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3709; 13053</t>
+          <t>3662; 12621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2285; 10208</t>
+          <t>2230; 10124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2992; 10524</t>
+          <t>2663; 10802</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3948; 12994</t>
+          <t>4015; 13826</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2876; 11786</t>
+          <t>2697; 12080</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11878; 28059</t>
+          <t>11800; 28601</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8419; 20154</t>
+          <t>8456; 21521</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13824; 28060</t>
+          <t>14176; 28854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7871; 20431</t>
+          <t>8401; 22485</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16593; 35355</t>
+          <t>16409; 34613</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1359; 7772</t>
+          <t>1357; 7644</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4046</t>
+          <t>0; 3616</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>615; 6044</t>
+          <t>623; 6329</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>658; 6011</t>
+          <t>648; 6107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4098; 12736</t>
+          <t>4070; 13022</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>983; 7549</t>
+          <t>978; 8503</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2147; 10270</t>
+          <t>2112; 10718</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2387; 10134</t>
+          <t>2467; 10644</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7387; 17819</t>
+          <t>7238; 17786</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1432; 8858</t>
+          <t>1455; 8737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3890; 13382</t>
+          <t>3412; 13013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4296; 13819</t>
+          <t>4119; 13405</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29827; 48869</t>
+          <t>30243; 50275</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22595; 41834</t>
+          <t>21828; 40283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23419; 40785</t>
+          <t>22524; 42130</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26689; 47882</t>
+          <t>27071; 47642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35479; 56781</t>
+          <t>36353; 57079</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32140; 53684</t>
+          <t>32407; 53422</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25557; 43287</t>
+          <t>24588; 43824</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>50321; 80682</t>
+          <t>49397; 79869</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70806; 99727</t>
+          <t>69665; 98791</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60111; 88177</t>
+          <t>60181; 87834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52722; 78920</t>
+          <t>53434; 79263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81694; 118814</t>
+          <t>81496; 117534</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 13,01</t>
+          <t>1,4; 8,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 10,15</t>
+          <t>0,7; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 13,44</t>
+          <t>0,74; 6,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,21</t>
+          <t>5,01; 15,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,58</t>
+          <t>4,91; 13,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,23</t>
+          <t>1,81; 10,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,64</t>
+          <t>3,39; 13,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 13,38</t>
+          <t>2,92; 11,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,47</t>
+          <t>3,83; 9,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,48</t>
+          <t>1,6; 7,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,38</t>
+          <t>2,68; 8,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,77</t>
+          <t>4,74; 11,65</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,61</t>
+          <t>3,32; 11,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,67</t>
+          <t>1,36; 8,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,15</t>
+          <t>2,41; 10,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,26</t>
+          <t>3,88; 15,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,0</t>
+          <t>3,74; 13,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,31</t>
+          <t>0,84; 7,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,49</t>
+          <t>0,59; 6,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 14,82</t>
+          <t>1,69; 10,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,62</t>
+          <t>4,49; 11,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,22</t>
+          <t>1,81; 6,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,42</t>
+          <t>2,19; 6,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,42</t>
+          <t>3,78; 11,8</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,09</t>
+          <t>4,95; 14,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,25</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,12</t>
+          <t>1,93; 11,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 16,02</t>
+          <t>3,07; 17,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,46</t>
+          <t>1,96; 11,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,93; 9,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,08</t>
+          <t>0,91; 8,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 18,64</t>
+          <t>2,98; 16,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,91</t>
+          <t>4,58; 11,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,49</t>
+          <t>1,19; 5,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,72</t>
+          <t>1,96; 7,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 14,3</t>
+          <t>4,27; 13,99</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,85</t>
+          <t>3,75; 9,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,19</t>
+          <t>7,53; 14,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,83</t>
+          <t>2,65; 7,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,33</t>
+          <t>3,9; 10,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,45</t>
+          <t>2,28; 7,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,39</t>
+          <t>1,8; 6,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,8</t>
+          <t>2,92; 7,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 10,56</t>
+          <t>5,25; 12,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,22</t>
+          <t>3,72; 7,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,53</t>
+          <t>5,3; 9,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,06</t>
+          <t>3,19; 6,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,28</t>
+          <t>5,38; 10,45</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,63</t>
+          <t>2,05; 8,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,35</t>
+          <t>2,8; 9,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,27</t>
+          <t>1,99; 8,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,52</t>
+          <t>6,84; 15,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,49</t>
+          <t>4,34; 12,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,89</t>
+          <t>5,48; 13,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,44</t>
+          <t>2,74; 9,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 17,63</t>
+          <t>1,87; 8,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,3</t>
+          <t>3,7; 8,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,98</t>
+          <t>4,72; 9,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,05</t>
+          <t>2,95; 7,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,32</t>
+          <t>5,19; 10,99</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,84%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,21</t>
+          <t>5,56; 17,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>1,29; 10,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,36</t>
+          <t>3,15; 14,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,86</t>
+          <t>3,77; 16,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 17,99</t>
+          <t>1,84; 10,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,48</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 15,8</t>
+          <t>1,02; 11,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 14,78</t>
+          <t>1,04; 8,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,08</t>
+          <t>4,61; 11,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,83</t>
+          <t>0,89; 6,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,09</t>
+          <t>2,94; 9,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,51</t>
+          <t>3,3; 10,62</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,54%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,87</t>
+          <t>5,21; 8,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,98</t>
+          <t>4,53; 7,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,27</t>
+          <t>3,51; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,26</t>
+          <t>6,58; 10,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,34</t>
+          <t>4,63; 7,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,49</t>
+          <t>3,28; 5,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,17</t>
+          <t>3,54; 6,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,69</t>
+          <t>4,55; 7,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,46</t>
+          <t>5,39; 7,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,33</t>
+          <t>4,4; 6,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,74</t>
+          <t>3,79; 5,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,38</t>
+          <t>6,19; 8,68</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10826</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>8661</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4271</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6186</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2616</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17114</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4629; 13575</t>
+          <t>1361; 8513</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1803; 8979</t>
+          <t>625; 5744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2821; 11167</t>
+          <t>739; 6831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2873; 10581</t>
+          <t>6120; 18357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1386; 8366</t>
+          <t>5124; 14204</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>617; 5595</t>
+          <t>1602; 8931</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>658; 6627</t>
+          <t>2813; 11427</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5922; 18265</t>
+          <t>2983; 11419</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8009; 19113</t>
+          <t>7742; 19608</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2786; 11556</t>
+          <t>2850; 12629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4727; 15322</t>
+          <t>4905; 15688</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10725; 25860</t>
+          <t>10626; 26140</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5759</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7815</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2897</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2787</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4704</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5759</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5795</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12629</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3611; 11890</t>
+          <t>2858; 10112</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>704; 7064</t>
+          <t>1309; 7690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>649; 6501</t>
+          <t>2720; 11314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1961; 9718</t>
+          <t>3543; 14168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2570; 10316</t>
+          <t>3265; 11678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1478; 7986</t>
+          <t>771; 7175</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2353; 10705</t>
+          <t>624; 6434</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3475; 14165</t>
+          <t>1628; 10288</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7785; 18408</t>
+          <t>7791; 19596</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3384; 11700</t>
+          <t>3399; 11760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4793; 14034</t>
+          <t>4780; 14955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6996; 19828</t>
+          <t>7106; 22172</t>
         </is>
       </c>
     </row>
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4751</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3903</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2857</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1808</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9151</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8796</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1364; 7472</t>
+          <t>4919; 14658</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>785; 6945</t>
+          <t>0; 5052</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>547; 5020</t>
+          <t>1459; 8824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1403; 8307</t>
+          <t>1748; 9835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4885; 14368</t>
+          <t>1324; 7623</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5166</t>
+          <t>787; 7730</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1892; 8356</t>
+          <t>564; 5182</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2007; 11901</t>
+          <t>1594; 8968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7825; 19864</t>
+          <t>7636; 19226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2040; 9385</t>
+          <t>2040; 8954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2687; 10596</t>
+          <t>2692; 10680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5016; 16552</t>
+          <t>4712; 15452</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12699</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24224</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13809</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7072</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11195</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12699</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24224</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9928</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>28461</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4525; 13746</t>
+          <t>7576; 18643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3441; 12734</t>
+          <t>17077; 32687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6861; 17504</t>
+          <t>5581; 16436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8520; 22513</t>
+          <t>7839; 21671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8007; 19101</t>
+          <t>4570; 14067</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17371; 32655</t>
+          <t>3710; 13152</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5625; 16454</t>
+          <t>6528; 16900</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8513; 22941</t>
+          <t>9390; 22068</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14422; 29080</t>
+          <t>14996; 28962</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23136; 41230</t>
+          <t>22906; 41178</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15051; 30692</t>
+          <t>13852; 29170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20282; 40399</t>
+          <t>20447; 39675</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7539</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15550</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7864</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12634</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7271</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5793</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7539</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6242</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>20743</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4433; 13150</t>
+          <t>2611; 10624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7354; 19912</t>
+          <t>3913; 12717</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3662; 12621</t>
+          <t>2851; 11713</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2230; 10124</t>
+          <t>10119; 23233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2663; 10802</t>
+          <t>4521; 12765</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4015; 13826</t>
+          <t>8180; 20563</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2697; 12080</t>
+          <t>3732; 12448</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11800; 28601</t>
+          <t>2205; 10311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8456; 21521</t>
+          <t>8564; 20146</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14176; 28854</t>
+          <t>13645; 28475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8401; 22485</t>
+          <t>8239; 20609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16409; 34613</t>
+          <t>13821; 29232</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3622</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2238</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7955</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3075</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8350</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1357; 7644</t>
+          <t>4027; 12812</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3616</t>
+          <t>956; 7540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>623; 6329</t>
+          <t>2136; 9810</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>648; 6107</t>
+          <t>2574; 11215</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4070; 13022</t>
+          <t>1378; 8137</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>978; 8503</t>
+          <t>0; 4330</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2112; 10718</t>
+          <t>623; 7022</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2467; 10644</t>
+          <t>731; 6061</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7238; 17786</t>
+          <t>6782; 17206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1455; 8737</t>
+          <t>1138; 8524</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3412; 13013</t>
+          <t>3790; 12784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4119; 13405</t>
+          <t>4576; 14718</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>45430</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>42275</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>33914</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>39057</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>30550</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>31485</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>36129</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45430</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>42275</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>33914</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98764</t>
+          <t>96093</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30243; 50275</t>
+          <t>35670; 56776</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21828; 40283</t>
+          <t>32330; 53434</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22524; 42130</t>
+          <t>24881; 44055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27071; 47642</t>
+          <t>45281; 73846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36353; 57079</t>
+          <t>29598; 49302</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32407; 53422</t>
+          <t>22086; 39809</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24588; 43824</t>
+          <t>23787; 42034</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49397; 79869</t>
+          <t>28201; 48875</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>69665; 98791</t>
+          <t>71298; 99671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60181; 87834</t>
+          <t>61076; 88081</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53434; 79263</t>
+          <t>52315; 79790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81496; 117534</t>
+          <t>80890; 113467</t>
         </is>
       </c>
     </row>
